--- a/data_agent/fundamentals/screener_data/NESTLEIND.xlsx
+++ b/data_agent/fundamentals/screener_data/NESTLEIND.xlsx
@@ -4054,7 +4054,7 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>1515.95</v>
+        <v>1500.20</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -4062,7 +4062,7 @@
         <v>79</v>
       </c>
       <c r="B9">
-        <v>292322.88</v>
+        <v>291198.82</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
